--- a/results/GSEA/glass_GSEA_Hallmark.xlsx
+++ b/results/GSEA/glass_GSEA_Hallmark.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>PATHWAY</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NES</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>NOMINAL_P</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>FDR</t>
         </is>

--- a/results/GSEA/glass_GSEA_Hallmark.xlsx
+++ b/results/GSEA/glass_GSEA_Hallmark.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PATHWAY</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>NES</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>NOMINAL_P</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FDR</t>
         </is>

--- a/results/GSEA/glass_GSEA_Hallmark.xlsx
+++ b/results/GSEA/glass_GSEA_Hallmark.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>PATHWAY</t>
   </si>
@@ -28,6 +28,9 @@
     <t>FDR</t>
   </si>
   <si>
+    <t>LEADING_EDGE_GENES</t>
+  </si>
+  <si>
     <t>E2F Targets</t>
   </si>
   <si>
@@ -176,6 +179,156 @@
   </si>
   <si>
     <t>Allograft Rejection</t>
+  </si>
+  <si>
+    <t>CDK1;DLGAP5;TACC3;CCNB2;CDKN2C;SPC25;DEPDC1;CDKN3;HELLS;PLK1;ATAD2;WEE1;GINS1;BIRC5;KIF18B;BUB1B;RRM2;TOP2A;DNMT1;HMMR;MAD2L1;ORC6;MKI67;PTTG1;LMNB1;DSCC1;AURKA;TIMELESS;CENPE;MYBL2;MELK;KIF4A;EZH2;CKS2;ING3;SMC4;NAA38;GINS3;CDCA8;UBE2T;AURKB;PLK4;HMGB2;TRIP13;CDC20;KPNA2;KIF2C;CDC25A;RAD51AP1;RFC3;MCM6;RFC2;CENPM;DONSON;BRCA2;DCTPP1;SPC24;NASP;CHEK2;PRIM2;ASF1B;ESPL1;PRKDC;SPAG5;TMPO;HMGB3;CKS1B;BARD1;TFRC;RACGAP1;SSRP1;RANBP1;DIAPH3;CTPS1;UBE2S;PAICS;CDK4;KIF22;NME1;TCF19;MLH1;DCLRE1B;NBN;RAN;E2F8;MCM4;TRA2B;ILF3;CDCA3;IPO7;MCM2;RPA3;EXOSC8;SYNCRIP;CHEK1;TK1;MCM3;CCNE1;PCNA;LBR;NUP205;TUBB;RNASEH2A;DCK;PMS2;SRSF2;MYC;SLBP;USP1;TP53;NOP56;GINS4;PA2G4;XPO1;MXD3;POLD2;POLE;RBBP7;BRCA1;ORC2;TUBG1;TIPIN;MCM7;TBRG4;HNRNPD;PRPS1;AK2;GSPT1;POLD3;EED;SNRPB;PHF5A;CBX5;SRSF1;MTHFD2;PPM1D;PSMC3IP;MMS22L;RAD1;PRDX4;SMC6;MSH2;UBR7;PPP1R8;RPA1;RPA2;SMC1A;POLA2;DEK;XRCC6;RAD51C</t>
+  </si>
+  <si>
+    <t>CDK1;PBK;HIF1A;TACC3;CDC7;KIF23;CCNA2;CCNB2;CDKN2C;NUSAP1;BUB1;CENPA;CDKN3;KIF15;CDC45;PLK1;NEK2;UBE2C;BIRC5;TOP2A;SLC7A5;HMMR;TTK;NDC80;FBXO5;MAD2L1;ORC6;MKI67;PTTG1;LMNB1;TPX2;AURKA;POLQ;CENPE;MYBL2;SNRPD1;DTYMK;MARCKS;CENPF;KIF4A;EZH2;CKS2;EXO1;TROAP;SLC7A1;SMC4;ODC1;AURKB;KIF11;PLK4;DBF4;CDC20;KPNA2;KIF2C;CDC25A;MCM6;PRC1;E2F2;BRCA2;NASP;PRIM2;ESPL1;TMPO;HMGB3;GINS2;CKS1B;BARD1;RAD54L;RACGAP1;CHAF1A;SFPQ;UBE2S;DKC1;CDK4;E2F3;KIF22;STIL;CCNF;TRAIP;SRSF10;TRA2B;ILF3;HMGN2;RBL1;MCM2;SYNCRIP;UCK2;MTF2;CHEK1;MCM3;G3BP1;LBR;SQLE;SRSF2;MYC;TOP1;FANCC;SS18;XPO1;ODF2;CDC6;TFDP1;POLE;KIF20B;DR1;PRMT5;KPNB1;CDC27;HNRNPD;SMC2;NCL;MT2A;GSPT1;E2F1;SRSF1;WRN;NUP50;LIG3;CUL1;RPA2;HNRNPU</t>
+  </si>
+  <si>
+    <t>CCNA2;CDC45;MAD2L1;HNRNPA2B1;SNRPD1;ILF2;CDK2;CBX3;ODC1;C1QBP;PPM1G;RFC4;CDC20;KPNA2;PRPF31;MCM6;NCBP2;CCT2;UBE2E1;SNRPA1;RANBP1;AIMP2;CTPS1;TYMS;HSPE1;CDK4;CCT3;ERH;APEX1;NME1;SRSF3;RAN;HNRNPA1;MCM4;TRA2B;YWHAE;HSPD1;NOP16;RRM1;MRPL9;MCM2;SNRPG;SYNCRIP;HNRNPR;EIF4A1;PSMA2;SET;G3BP1;LSM7;FBL;HNRNPC;PCNA;SNRPD3;SSBP1;U2AF1;SRSF2;MYC;CSTF2;SERBP1;USP1;NOP56;LSM2;EIF4G2;CCT5;PA2G4;RUVBL2;EIF4E;EIF3B;UBA2;XPO1;CLNS1A;SRM;TFDP1;RPLP0;VBP1;POLD2;GNL3;HDGF;PWP1;RPS2;ORC2;TUFM;MCM7;KPNB1;PSMD14;PPIA;HNRNPD;HNRNPA3;SF3B3;GSPT1;TRIM28;RRP9;SRSF1;HDAC2;STARD7;PRDX4;CAD;CCT4;FAM120A;PSMA1;RNPS1;DHX15;PSMA7;SRPK1;CUL1;PTGES3;HNRNPU;PHB2;GLO1;TARDBP;SRSF7;NPM1;PSMC6;DEK;XRCC6;EIF1AX;PSMB2;SNRPD2;CCT7;IFRD1;TXNL4A;ABCE1;SSB;NCBP1;CANX;MCM5;RPS5;EIF2S1;COPS5;CYC1;DUT;RPS10;SLC25A3;SNRPB2;PABPC4;SNRPA;PABPC1;POLE3</t>
+  </si>
+  <si>
+    <t>PNP;ZWINT;RFC4;RAD51;RFC3;NCBP2;RFC2;POLR1C;ERCC8;NME4;SSRP1;TYMS;PRIM1;NME1;ALYREF;ZNRD1;GTF2A2;RFC5;POLR2D;SRSF6;RPA3;PCNA;POLR2H;TP53;SF3A3;TAF13;TARBP2;SMAD5;UMPS;POLA1;POLR2J;GTF2H3;TAF12;ERCC1;VPS37B;ADCY6;RAE1;POLD3;TAF1C;NT5C3A;NELFCD;SEC61A1;MPC2;SDCBP;ERCC4;ERCC2;NPR2;ARL6IP1;RPA2;DGCR8;POM121;RALA;POLA2;VPS37D;GTF2B;POLR2G;PDE4B;POLD1;LIG1;DCTN4;POLH;GTF2H1;DUT;CSTF3;ITPA;POLR2F;NUDT9;DGUOK;TAF9;CDA;POLB;IMPDH2;SUPT4H1;TSG101;REV3L;AGO4;FEN1;POLR2K;BCAM;CLP1;VPS28;POLR3GL;TMED2;MPG;NELFE;TAF6;MRPL40</t>
+  </si>
+  <si>
+    <t>MAST3;NRIP2;RYR2;CPB1;ADRA2C;NOS1;THNSL2;ARHGDIG;CPEB3;MFSD6;SYNPO;EFHD1;SNCB;RGS11;DTNB;ITIH3;NGB;SOX10;KCNN1;RSAD2;FGF22;GDNF;SLC30A3;MYOT;MYO15A;COPZ2;SLC29A3;MX1;CAPN9;UPK3B;P2RX6;SIDT1;PLAG1;THRB;CAMK1D;IFI44L;TENM2;EGF;CCNA1;DLK2</t>
+  </si>
+  <si>
+    <t>LDB3;SCD;GSN;SOD3;PVALB;MYLK;TNNT2;FABP3;NQO1;NOS1;KCNH1;TPD52L1;APLNR;FOXO4;SGCD;MYL3;HSPB2;CFD;MYH11;GNAO1;FXYD1;PRNP;MAPRE3;ACSL1;PC;HDAC5;BIN1;ERBB3;APOD;PPP1R3C;MYOM1;CDH13;AK1;LSP1;TNNI2;TNNT1;PPFIA4;COL15A1;SYNGR2;CKMT2;CAMK2B;PYGM;COX7A1;HSPB8;DAPK2;PICK1;IGF1;MEF2C;LPIN1</t>
+  </si>
+  <si>
+    <t>PLK1;TMEM97;PRMT3;CBX3;PLK4;DCTPP1;AIMP2;HSPE1;CDK4;MCM4;HSPD1;NOP16;MRTO4;MYC;NOP56;BYSL;PA2G4;SRM;NIP7;GNL3;TFB2M;WDR43;TBRG4;GRWD1;RRP9;NPM1;NOP2;PPAN;MCM5;SLC19A1;IMP4;RABEPK;UTP20</t>
+  </si>
+  <si>
+    <t>SLC25A5;ETFA;CYCS;NNT;FXN;DECR1;IDH1;DLD;TIMM50;MRPS11;OXA1L;FDX1;NDUFA7;MDH2;SDHC;TIMM13;CS;DLST;ATP6V1G1;UQCRFS1;TOMM22;ABCB7;NDUFB5;ACADM;NDUFB6;NDUFA6;PMPCA;MRPL15;UQCRH;MRPL11;NDUFA5;NDUFS3;MTRF1;HSD17B10;TIMM9;FH;MRPS12;TIMM8B;ECI1;BAX;PDHB;UQCR11;MRPL35;PHB2;LDHB;HTRA2;NDUFC2;COX7B;DLAT;NDUFA4;SDHD;TIMM17A;MRPS15;NDUFB3;NDUFB2;COX10;IDH3B;SLC25A20;NDUFS6;CYC1;SLC25A3;UQCRC1;AIFM1;POLR2F;NDUFS4;NDUFS2;SUCLG1;MRPS22;HCCS;NDUFV2;UQCRC2;COX11;POR;ACAA1;GRPEL1;NDUFC1;SDHB;IMMT;IDH2;BDH2;PDHA1;UQCR10;ISCA1;HADHA;RHOT1;SLC25A6;COX7A2;LDHA;COX8A;HADHB;NDUFAB1;NDUFS1;CYB5A;COX7C;PRDX3;MRPS30;NDUFB7;MPC1;ECH1;COX6B1;RHOT2;LRPPRC;VDAC1;NDUFB1;UQCRQ;AFG3L2;HSPA9;COX6C;NDUFA9</t>
+  </si>
+  <si>
+    <t>ARAP3;CDK1;DLGAP5;KIF23;CCNB2;NUSAP1;BUB1;KIF15;PLK1;NEK2;BIRC5;TOP2A;TTK;NDC80;FBXO5;ECT2;LMNB1;TPX2;AURKA;CENPE;MID1;MARCKS;CENPF;KIF4A;TRIO;SMC4;KNTC1;PLEKHG2;KIF11;KIF2C;PRC1;BRCA2;ESPL1;RACGAP1;NEDD9;KIF22;MAPRE1;PIF1;YWHAE;OPHN1</t>
+  </si>
+  <si>
+    <t>IFIT2;NCOA7;CNP;IFIT3;TMEM140;SLC25A28;RSAD2;IFI27;CMPK2;GMPR;LY6E;TXNIP;OASL;ISG20;MX1;IRF7;RTP4;OAS1;LGALS3BP;IFITM2;TDRD7;IFI44L;HERC6;DHX58;IRF9;IFITM3;BATF2;C1S;EPSTI1;IFITM1;ISG15;BST2</t>
+  </si>
+  <si>
+    <t>STARD4;BUB1;MTHFD2L;PLK1;RRM2;SLC7A5;HMGCS1;TMEM97;PNP;AURKA;CDC25A;DHFR;TFRC;IDH1;CYP51A1;HSPE1;LDLR;PSME3;CCNF;RDH11;MCM4;HSPD1;STC1;CCT6A;MCM2;FADS2;NUP205;SQLE;PGM1;RIT1;PNO1;EBP;SEC11A;TUBG1;GSK3B;PSMD14;PPIA;ABCF2;HMBS;TCEA1;TOMM40;CALR;PDAP1;RRP9;ACTR3;HMGCR;MTHFD2;GMPS;SERPINH1;BCAT1;ACLY;NFYC;SSR1;SHMT2;RPA1;ACSL3;SLC37A4;PSMA3;NAMPT;FGL2;ELOVL5;PSMC6;CTH;PSMD13;IFRD1;PIK3R3;CANX;DDX39A;COPS5;GTF2H1;YKT6;FADS1;ATP2A2;PSMC2;TES</t>
+  </si>
+  <si>
+    <t>HEYL;JAG1;LFNG;APH1A;NOTCH1;WNT5A;NOTCH3;PPARD;MAML2;HES1;TCF7L2;FZD1;PSEN2;CUL1;SKP1;NOTCH2;FZD5;ST3GAL6;KAT2A;FZD7</t>
+  </si>
+  <si>
+    <t>TMCC2;OPTN;KEL;ACP5;SNCA;DMTN;ALAD;MXI1;FN3K;ENDOD1;SELENBP1;CPOX;AGPAT4;FTCD;ANK1;CCDC28A;PC;UROS;ALAS2;PDZK1IP1;EPOR;NEK7;HEBP1;OSBP2;SPTB;GYPC;XK;EZH1;ATP6V0A1;MGST3;HTATIP2;TRIM58;RHCE;BTRC;BLVRB;LAMP2;MPP1;NFE2L1;RAP1GAP;FBXO7;ADIPOR1;P4HA2;AQP3;HAGH;CA1;NCOA4;SLC10A3</t>
+  </si>
+  <si>
+    <t>RAB31;SMAD1;ID3;FKBP1A;HDAC1;SKIL;KLF10;CTNNB1;LEFTY2;IFNGR2;ID2;SMURF2;BMPR1A;RHOA;ID1;BMP2;ENG;XIAP;BMPR2;CDK9;PPP1CA;TGIF1;SKI;TRIM33;SLC20A1;NCOR2;WWTR1;TGFB1;PMEPA1;UBE2D3;MAP3K7;SMURF1</t>
+  </si>
+  <si>
+    <t>KCNJ8;SLCO2A1;LPL;JAG1;VCAN;STC1;CCND2;ITGAV;VAV2;FSTL1;TNFRSF21;LUM;COL5A2;MSX1;NRP1;PDGFA;OLR1;POSTN;PF4</t>
+  </si>
+  <si>
+    <t>HEY1;NOTCH4;LEF1;JAG1;NOTCH1;PPARD;SKP2;CCND2;MYC;TP53;CTNNB1;DVL2;FZD1;HDAC2;PSEN2;CUL1;ADAM17;MAML1;AXIN2;CSNK1E;NCSTN;HEY2;PTCH1;KAT2A;NCOR2</t>
+  </si>
+  <si>
+    <t>GLDC;STARD4;HMGCS1;TMEM97;ANXA5;LPL;JAG1;FDPS;ACAT2;TP53INP1;CYP51A1;LDLR;FADS2;SQLE;GSTM2;EBP;ETHE1;CTNNB1;TNFRSF12A;AVPR1A;HMGCR;CBS</t>
+  </si>
+  <si>
+    <t>IGFBP1;SLC7A5;FUS;CKS1B;DKC1;EIF4A1;NOP56;LSM1;SPCS1;EIF4E;SEC11A;TATDN2;PDIA6;GEMIN4;EIF4G1;KHSRP;PAIP1;BANF1;CALR;RRP9;EXOSC9;MTHFD2;SLC30A5;EIF4A3;SSR1;CNOT6;SRPRB;NPM1;EXOSC2;GOSR2;NOP14;EIF2S1;SPCS3;CNOT4;LSM4;POP4;CNOT2;PARN;FKBP14;DCP1A;NHP2;CXXC1;EIF2AK3;SHC1;CEBPG</t>
+  </si>
+  <si>
+    <t>P2RY2;SEMA3B;TMPRSS3;SH3BP5;TPD52L1;CALB2;ALDH3B1;SFN;CXCL12;INPP5F;NBL1;ENDOD1;MLPH;DEPTOR;RPS6KA2;FLNB;OLFM1;ITPK1;SYNGR1;ADD3;KRT8;RHOD;CYP26B1;GAB2;ASB13;WWC1;SYT12;SLC7A2;NPY1R;SLC9A3R1;BCL2;BLVRB;ZNF185;HSPB8;KRT18;DHRS3;HR;CBFA2T3;RAPGEFL1;AQP3</t>
+  </si>
+  <si>
+    <t>CDK1;CCNB2;BUB1;CDKN3;ARL4A;NEK2;TTK;AURKA;EZH2;GRM8;NCAPH;SPATA6;TKTL1;DBF4;RFC4;KIF2C</t>
+  </si>
+  <si>
+    <t>MBP;NQO1;PRNP;FTL;MGST1;CDKN2D;IPCEF1;PFKP;LSP1</t>
+  </si>
+  <si>
+    <t>CDK1;CENPA;DEPDC1;KIF20A;HMMR;PGM2;AURKA;TKTL1;VCAN;SDC3;NASP;PAXIP1;ME2;IDH1;CASP6;CAPN5;TPST1;STC1;DLD;SOX9;EGFR;POLR3K;NANP;TSTA3;MDH2;HS2ST1;GPC1;COG2;SDHC;IGFBP3;B4GALT4;DCN;HS6ST2;GALK1;PPIA;PRPS1;BPNT1;IDUA;CHST2;SLC37A4;SLC35A3;CTH;AGRN;COPB2;RPE;TGFBI;PMM2;PPP2CB;EXT1;ALG1;GUSB;ALDH7A1;EXT2;PSMC4;NDUFV3;MED24;GNPDA1</t>
+  </si>
+  <si>
+    <t>CDK1;VAV3;CDK2;RAF1;CDK4;PLCG1;EGFR;TNFRSF1A;RIPK1;RIT1;EIF4E;CSNK2B;GSK3B;UBE2N;CALR;E2F1;ACTR3;MAPKAP1;MAP2K6;PRKAR2A;IRAK4;RPS6KA3;PRKAG1;PFN1;RAC1;AKT1;MYD88</t>
+  </si>
+  <si>
+    <t>ABCB4;ABCD3;TOP2A;ECI2;ABCB1;FDPS;ABCD2;GSTK1;IDH1;NUDT19;CTPS1;RDH11;SCP2;PEX13;BCL10;ERCC1;GNPAT;SLC25A17;ACOX1;MSH2;SIAH1;PEX2;ELOVL5;ISOC1;PEX11A;FADS1;ESR2;PABPC1;CNBP;CRAT;SMARCC1;ACAA1;CEL</t>
+  </si>
+  <si>
+    <t>OPTN;RXRG;PAOX;CYP27A1;ABCA2;SLCO1A2;LIPE;ALDH8A1;ABCA5;ACSL1;ABCA8;CYP7B1;NPC1;ABCA6;LCK;NR3C2;ALDH1A1;SLC22A18;CH25H</t>
+  </si>
+  <si>
+    <t>DBI;HMGCS1;GNAI3;SLC26A2;UBE2I;CENPN;PDLIM5;ITGAV;LIFR;PA2G4;ABCC4;ZBTB10;UBE2J1;HMGCR;IQGAP2;RPS6KA3;HPGD;ACSL3;NGLY1;ELOVL5;XRCC6;AKT1;RAB4A;XRCC5;SRP19;SPCS3;GPD1L;ABHD2;FADS1;PGM3;MYL12A;INSIG1;FKBP5;PTPN21;SORD;CDK6;TMEM50A;VAPA;ADAMTS1;SEC24D;PMEPA1</t>
+  </si>
+  <si>
+    <t>SOCS2;ARL4A;SPRY4;PNP;BATF3;ABCB1;SPRED2;ODC1;TNFRSF4;CASP3;DCPS;PHLDA1;ITGAE;RGS16;HOPX;AGER;TWSG1;ADAM19;EMP1;F2RL2;CCND2;UCK2;CCNE1;ITGAV;MYC;IL3RA;CDC6;UMPS;GPR65;COCH;CYFIP1;AHCY;TNFRSF21;LCLAT1;GLIPR2;FLT3LG;IL1RL1;LIF;FGL2;WLS;TTC39B;BMP2;SNX14;NOP2;TNFSF10;BMPR2;MAPKAPK2;PLSCR1;NRP1;CISH;SERPINB6;PDCD2L;CKAP4;IL4R;LRIG1;PTCH1;NT5E;SOCS1;ETV4;PRAF2;NFIL3;NCOA3;ITGA6</t>
+  </si>
+  <si>
+    <t>LXN;PLAC8;IGFBP1;PGM2;ETS1;BCAN;GCNT2;TKTL1;F3;SDC3;NCAN;MAP3K1;VHL;CASP6;PGF;HS3ST1;SRPX;STC1;CSRP2;EGFR;ACKR3;PGM1;GPC1</t>
+  </si>
+  <si>
+    <t>F2R;PDGFRB;WEE1;TOP2A;LEF1;CDK2;BTG3;CASP3;HMGB2;CASP2;PLAT;BID;NEDD9;CASP6;DIABLO;EMP1;PRF1;CCND2;EBP;CTNNB1;BCL10;DCN;BRCA1;MCL1;TNFRSF12A;AVPR1A;CD69;GSTM1;PSEN2;BAX;CREBBP;CTH;BMP2;LUM;TNFSF10;XIAP;EREG;DAP;DAP3;GADD45A;TIMP3</t>
+  </si>
+  <si>
+    <t>MATN3;PDGFRB;CDH6;COL4A1;GPX7;COL4A2;VCAN;LAMA2;CDH2;GAS1;WNT5A;MEST;SPARC;CALD1;NID2;PCOLCE2;FERMT2;PRRX1;ITGAV;GPC1;BMP1;LAMC1;IGFBP3;ELN;CDH11;LAMA1;PPIB;DCN;DPYSL3;FSTL1;IGFBP2;SGCB;MCM7;TNFRSF12A;ID2;PTX3;SERPINH1;MMP14;CALU;LUM;HTRA1;NOTCH2;COL5A2;TGFBI;THY1;MSX1;SNAI2;GADD45A;TIMP3;NNMT;MATN2;OXTR;MMP2;MXRA5;FN1;ECM2;ANPEP;ITGA5</t>
+  </si>
+  <si>
+    <t>CDKN2C;ARL4A;COL4A1;LPL;LAMA4;SLC5A6;FZD4;DECR1;IDH1;SAMM50;MAP4K3;DLD;SCP2;DHRS7B;LIFR;PGM1;MDH2;SDHC;PPP1R15B;HADH;ITGA7;CS;COQ9;ADCY6;PTCD3;ACADM;MRPL15;CPT2;MCCC1;AK2;TANK;ACOX1;NDUFA5;NDUFS3;SOWAHC;JAGN1;ACLY;DGAT1;UQCR11;ATL2;CD302;COX7B;PEMT;DLAT;CYC1;GADD45A;UQCRC1;SLC19A1;AIFM1;RIOK3;SUCLG1;ARAF;CRAT;POR;ELMOD3;GRPEL1;COQ3;MTCH2;HIBCH;COQ5;SDHB;RMDN3;LPCAT3;RAB34;IMMT</t>
+  </si>
+  <si>
+    <t>SST;CHGA;SYT13;STXBP1;PCSK2;PAK3;MAFB;PCSK1</t>
+  </si>
+  <si>
+    <t>IL17RB;PDGFC;TNFRSF1A;IL3RA;IFNGR2;CXCL3;TNFRSF12A;TNFRSF21;CBL;IFNAR1;SOCS3;STAM2;MYD88;TYK2;IL10RB;PTPN2;BAK1;CNTFR;ITGA4;IL4R;SOCS1;JUN;PF4;TGFB1;PTPN1;STAT3;IL6ST;IL7;CXCL11;PIM1;A2M;IFNGR1;CXCL13;IL6;IL13RA1;IL1B;ACVRL1;CD44;OSMR;CSF2RA;CXCL1</t>
+  </si>
+  <si>
+    <t>FLT4;ETV1;BPGM;TMEM100;ETS1;TRIB2;ABCB1;DUSP6;CROT;MMP9;PLAT;ZNF639;TSPAN13;YRDC;TFPI;MAP3K1;ACE;RGS16;AKT2;RBM4;SOX9;EMP1;CCND2;PRRX1;GNG11;TOR1AIP2;PRDM1;TMEM158;FBXO4;SPON1;IGFBP3</t>
+  </si>
+  <si>
+    <t>TNFSF9;KRT17;ZNF365;NUPR1;NDRG1;FGF13;OSGIN1;ALOX15B;TPD52L1;TGFA;SFN;TSPYL2;CCP110;EPHX1;PERP;STOM;PHLDA3;KIF13B;ERCC5;FUCA1;TXNIP;CDH13;AK1;GLS2;CTSD;BAIAP2</t>
+  </si>
+  <si>
+    <t>RAB31;KIF20A;TOP2A;SLC7A5;BTG3;SCUBE2;PLK4;PAPSS2;CDC20;FOXC1;TSPAN13;GINS2;MEST;IL17RB;SLC26A2;NXT1;STIL;RBBP8;DLG5;XRCC3;NRIP1;TSTA3;RNASEH2A;SERPINA1;GPER1;ASCL1;CDC6;UGDH;PDZK1</t>
+  </si>
+  <si>
+    <t>PTPRG;HMGCS1;ECI2;ADSL;ODC1;ACAT2;DECR1;IDH1;APEX1;RDH11;NBN;DLD;SUCLG2;MDH2;SDHC;HADH;CCDC58;UGDH;BCKDHB;DLST;OSTC;ACADM;SLC22A5;RDH16;CPT2;ACOX1;HSD17B10;NTHL1;FH;GCDH;G0S2;ECI1;PDHB;HPGD;ELOVL5;SDHD;CRYZ;BPHL;IDH3B</t>
+  </si>
+  <si>
+    <t>P2RY2;TNFSF9;BEST1;SLC31A2;SEMA4D;SCN1B;SGMS2;HPN;LPAR1;APLNR;CD55;ICOSLG;CCL5;RHOG;PSEN1</t>
+  </si>
+  <si>
+    <t>COL9A1;CDH6;CLDN5;LIMA1;VCAN;VWF;MPZL1;MMP9;SDC3;ARHGEF6;AKT2;PARD6G;PLCG1;ADAMTS5;ADAM9;ZYX;EGFR;ITGA10;NLGN3;WNK4;BMP1;CTNND1;THBS3;HADH;VAV2;CDH11;WASL;TUBG1;CD276;EXOC4;ARPC2;PBX2;INPPL1;CDK8;MYL12B;MVD;PFN1;AMH;MDK;TRO;PIK3R3;VASP;TGFBI;CD99;THY1;PARVA;MMP2;ADAM23;MYH10;CDH4;PECAM1;SPEG;CRAT;SHROOM2;MSN;RSU1;INSIG1;CD34</t>
+  </si>
+  <si>
+    <t>DUSP6;F3;MMP15;VWF;MMP9;PLAT;GNG12;P2RY1;SPARC;CAPN5;ADAM9;FYN;F2RL2;SH2B2;SERPINA1;APOC2;BMP1;LEFTY2;CTSO;PROS1;PDGFB;MMP14;RAC1;WDR1;HTRA1;CAPN2;MASP2;ARF4;MST1;TIMP3;GNB2;MMP2;FN1;PECAM1;ACOX2;CFH</t>
+  </si>
+  <si>
+    <t>MARCKS;JAG1;BTG3;F3;PHLDA1;YRDC;B4GALT5;LDLR;TNFAIP6;EDN1;PDLIM5;ACKR3;MYC;KLF10;DUSP5;FJX1;ZBTB10;HES1;GPR183;IFNGR2;MCL1;CXCL3;ID2;TANK;TRIP10;TNIP2;CD69;PTX3;G0S2;LIF;NAMPT;RCAN1;PTPRE;SOCS3;BMP2;PDE4B;BIRC2;GADD45A;TGIF1;BTG1;IER5;SLC16A6;ZFP36;EGR1;SIK1;KLF9;ZC3H12A;OLR1;NFKB1;RIPK2;JUN;TIPARP;NFIL3</t>
+  </si>
+  <si>
+    <t>HEY1;TLE1;OPHN1;NRCAM;CRMP1;TLE3;THY1;NRP1;GLI1;CNTFR;HEY2;PTCH1;CDK6;NKX6-1</t>
+  </si>
+  <si>
+    <t>TMX1;ERGIC3;EGFR;COG2;ATP6V1B1;RAB5A;ARFIP1;RPS6KA3;COPB2;GOSR2;ARFGEF1;TOM1L1;RER1;YKT6;COPB1;AP2S1;YIPF6;VAMP4;RAB14;ARFGAP3;BET1;TSG101;AP1G1;VPS45;TMED10;PAM;SEC24D;GNAS;CD63;TMED2;ANP32E;PPT1;SEC31A;RAB22A;GLA;COPE;ZW10;VAMP7;SNAP23;AP2M1;CLCN3</t>
+  </si>
+  <si>
+    <t>E2F5;GGH;SHOX2;CDK2;ABCB1;BTG3;CASP3;RFC4;CDO1;BID;TFRC;HYAL2;PPAT;CCNE1;POLR2H;CDC34;CHRNA5;IGFBP2;PDAP1;HSPA13;POLG2;DGAT1;HNRNPU;WIZ;MMP14;BMP2;APOM;SIGMAR1;MSX1;YKT6;BTG1;BAK1;POLE3;NAT1;AP2S1;DNAJB1;PPP1R2;LYN;ACAA1;GRPEL1;RASGRP1;UROD;TMBIM6;NKX2-5;CEBPG;TGFBRAP1;FEN1;PRPF3;DDX21;CLCN2;CDC5L;AGO2;RPN1;NXF1;DNAJA1;ONECUT1;PPT1;STIP1;BCL2L11</t>
+  </si>
+  <si>
+    <t>ENPEP;IGFBP1;TMEM97;GART;GCNT2;PAPSS2;CROT;ABCD2;CDO1;GSTM4;IDH1;CASP6;HGFAC;PPARD;SLC35B1;MCCC2;TPST1;SLC12A4;MTHFD1;PDLIM5;TNFRSF1A;UGDH;GSTT2;LEAP2;ID2;MT2A;AHCY;ACOX1;PROS1;BCAT1;ADH5;SHMT2;PTGES3;SLC35D1;ELOVL5;SAR1B;SERTAD1;PEMT;ASL;BPHL;HACL1;ACOX3;PYCR1;GSS;ATP2A2;AP4B1</t>
+  </si>
+  <si>
+    <t>AFAP1L2;GAS1;SRPX;GSTM3;BRCA1;EPHB4;FLOT2;THY1;AKAP7;SHROOM2;LYN;SULF2</t>
+  </si>
+  <si>
+    <t>PDGFRB;MMP16;SLC7A1;F3;SRI;HAS2;NFIB;TFPI;LDLR;MIOS;FYN;MTA1;PDLIM5;MYC;KIT;LAMC1;VAV2;BCKDHB</t>
+  </si>
+  <si>
+    <t>IFIT2;IFIT3;IFIT1;EIF4E3;SLC25A28;CCL5;RSAD2;ITGB7;IFI27;CMPK2;PFKP;LY6E;STAT4;CFB;TXNIP;OASL;ISG20;MX1;MVP;IRF7;RTP4;MX2;SLAMF7;LGALS3BP;IFITM2;GZMA;TDRD7;IFI44L;HERC6;DHX58;OAS2;IRF9;CCL7;IFITM3;BATF2;C1S;TNFAIP2;EPSTI1</t>
+  </si>
+  <si>
+    <t>ME1;CSRP1;CR1;CD55;HPCAL4;CCL5;RHOG;PSEN1;CP;GZMB;LIPA;PCLO;S100A13;CFB;CPM;CDH13;LCK;KLKB1;LGMN;IRF7;CTSD;F5;SPOCK2;PDP1;CPQ;LAMP2;CD59;GZMA;C4BPB;DOCK10;CEBPB;CALM3;KCNIP2;C1S;GZMK;PIK3R5;C2;PRSS3</t>
+  </si>
+  <si>
+    <t>F2R;HIF1A;IFNAR2;ETS1;GLMN;NOS2;MMP9;NME1;MRPL3;IKBKB;GALNT1;EGFR;PRF1;CCND2;BCL10;EIF5A;BRCA1;IFNGR2;GPR65;UBE2N;DEGS1;BCAT1;LIF;RPS3A;DYRK3;NPM1;AKT1;ABCE1;EREG;THY1;RPL39;NCK1;SRGN;TAP2;LYN;ST8SIA4;IL4R;INHBB;HDAC9;SOCS1;RIPK2;RPS19</t>
   </si>
 </sst>
 </file>
@@ -507,10 +660,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,10 +676,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>-3.160204987718735</v>
@@ -537,10 +693,13 @@
       <c r="D2">
         <v>2.71413760644434E-44</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>-2.887095594412404</v>
@@ -551,10 +710,13 @@
       <c r="D3">
         <v>6.533024483014562E-32</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>-2.753717283476824</v>
@@ -565,10 +727,13 @@
       <c r="D4">
         <v>5.524925173682399E-27</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>-1.9107510177618</v>
@@ -579,10 +744,13 @@
       <c r="D5">
         <v>3.785669971279379E-06</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>2.021821961848025</v>
@@ -593,10 +761,13 @@
       <c r="D6">
         <v>1.036299815660573E-05</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1.852663082352451</v>
@@ -607,10 +778,13 @@
       <c r="D7">
         <v>1.036299815660573E-05</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
         <v>-1.887909283556269</v>
@@ -621,10 +795,13 @@
       <c r="D8">
         <v>0.0003116461084881342</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>-1.669803396332565</v>
@@ -635,10 +812,13 @@
       <c r="D9">
         <v>0.0003116461084881342</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>-1.648381074792338</v>
@@ -649,10 +829,13 @@
       <c r="D10">
         <v>0.0004039477678294829</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>1.800210980041733</v>
@@ -663,10 +846,13 @@
       <c r="D11">
         <v>0.0008519756698058352</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
         <v>-1.613400063193003</v>
@@ -677,10 +863,13 @@
       <c r="D12">
         <v>0.00151241539158751</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13">
         <v>-1.840243193336268</v>
@@ -691,10 +880,13 @@
       <c r="D13">
         <v>0.003363761390903802</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14">
         <v>1.482313461656537</v>
@@ -705,10 +897,13 @@
       <c r="D14">
         <v>0.004747814199942005</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>-1.683286387336127</v>
@@ -719,10 +914,13 @@
       <c r="D15">
         <v>0.006667891067684972</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16">
         <v>-1.756645467012954</v>
@@ -733,10 +931,13 @@
       <c r="D16">
         <v>0.0137494298476205</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>-1.631613090556789</v>
@@ -747,10 +948,13 @@
       <c r="D17">
         <v>0.01968182724021788</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18">
         <v>-1.472663462603186</v>
@@ -761,10 +965,13 @@
       <c r="D18">
         <v>0.03135328882415022</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>-1.4362840111436</v>
@@ -775,10 +982,13 @@
       <c r="D19">
         <v>0.03350687348849353</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>1.245637886108382</v>
@@ -789,10 +999,13 @@
       <c r="D20">
         <v>0.08103898271040214</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21">
         <v>-1.355262172125226</v>
@@ -803,10 +1016,13 @@
       <c r="D21">
         <v>0.1079346557759627</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22">
         <v>1.35888051397703</v>
@@ -817,10 +1033,13 @@
       <c r="D22">
         <v>0.1510894189673778</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>-1.246810058599482</v>
@@ -831,10 +1050,13 @@
       <c r="D23">
         <v>0.1925610621262795</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>-1.228679864300095</v>
@@ -845,10 +1067,13 @@
       <c r="D24">
         <v>0.2942519405408148</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>-1.217401323194532</v>
@@ -859,10 +1084,13 @@
       <c r="D25">
         <v>0.3015312131919906</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26">
         <v>1.157018493059941</v>
@@ -873,10 +1101,13 @@
       <c r="D26">
         <v>0.3015312131919906</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>-1.152198417484091</v>
@@ -887,10 +1118,13 @@
       <c r="D27">
         <v>0.4263317135784358</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28">
         <v>-1.09225266892674</v>
@@ -901,10 +1135,13 @@
       <c r="D28">
         <v>0.513888888888889</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29">
         <v>-1.089224872702456</v>
@@ -915,10 +1152,13 @@
       <c r="D29">
         <v>0.513888888888889</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30">
         <v>-1.064224569367372</v>
@@ -929,10 +1169,13 @@
       <c r="D30">
         <v>0.5896852483883201</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>-1.063563216798272</v>
@@ -943,10 +1186,13 @@
       <c r="D31">
         <v>0.5896852483883201</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32">
         <v>-1.040862170908085</v>
@@ -957,10 +1203,13 @@
       <c r="D32">
         <v>0.6275398281008379</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33">
         <v>1.019212687250622</v>
@@ -971,10 +1220,13 @@
       <c r="D33">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34">
         <v>-1.016586658946231</v>
@@ -985,10 +1237,13 @@
       <c r="D34">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35">
         <v>-1.008004920217805</v>
@@ -999,10 +1254,13 @@
       <c r="D35">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36">
         <v>0.9995675097137058</v>
@@ -1013,10 +1271,13 @@
       <c r="D36">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37">
         <v>-0.9918543772413142</v>
@@ -1027,10 +1288,13 @@
       <c r="D37">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38">
         <v>-0.9916214635481546</v>
@@ -1041,10 +1305,13 @@
       <c r="D38">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39">
         <v>0.990500323445804</v>
@@ -1055,10 +1322,13 @@
       <c r="D39">
         <v>0.6457115009746589</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40">
         <v>-0.9660455887353179</v>
@@ -1069,10 +1339,13 @@
       <c r="D40">
         <v>0.693193837006546</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41">
         <v>-0.9301191614162955</v>
@@ -1083,10 +1356,13 @@
       <c r="D41">
         <v>0.7631578947368421</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42">
         <v>-0.9231661153650417</v>
@@ -1097,10 +1373,13 @@
       <c r="D42">
         <v>0.7648694908001711</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43">
         <v>-0.8896772230293513</v>
@@ -1111,10 +1390,13 @@
       <c r="D43">
         <v>0.7809013833110219</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>-0.8843058459831089</v>
@@ -1125,10 +1407,13 @@
       <c r="D44">
         <v>0.8066946065138194</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45">
         <v>-0.8591599041580645</v>
@@ -1139,10 +1424,13 @@
       <c r="D45">
         <v>0.8594237570210109</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46">
         <v>-0.8222231098134721</v>
@@ -1153,10 +1441,13 @@
       <c r="D46">
         <v>0.9269403759658631</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47">
         <v>-0.743520568348066</v>
@@ -1167,10 +1458,13 @@
       <c r="D47">
         <v>0.9269403759658631</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>-0.7714021662906997</v>
@@ -1181,10 +1475,13 @@
       <c r="D48">
         <v>0.9460034013605442</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49">
         <v>0.8735832632304252</v>
@@ -1195,10 +1492,13 @@
       <c r="D49">
         <v>0.9460034013605442</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50">
         <v>0.8224032990911349</v>
@@ -1209,10 +1509,13 @@
       <c r="D50">
         <v>0.9803921568627451</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51">
         <v>-0.6635536332186533</v>
@@ -1222,6 +1525,9 @@
       </c>
       <c r="D51">
         <v>0.9910414333706606</v>
+      </c>
+      <c r="E51" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
